--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="229">
   <si>
     <t xml:space="preserve">Οδηγία NIS2 (ΕΕ) 2022/2555 και Microsoft 365: checklist</t>
   </si>
@@ -58,6 +58,45 @@
   </si>
   <si>
     <t xml:space="preserve">Η Οδηγία μεταφέρθηκε στην ελληνική νομοθεσία με τον ν. 5160/2024 και τα μέτρα εξειδικεύονται από την ΚΥΑ 1689/2025. Ο έλεγχος στην Ελλάδα γίνεται με βάση την ΚΥΑ. Το αναλυτικό checklist των 111 απαιτήσεών της βρίσκεται στο https://thecybersec.gr/kya-1689-2025/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πνευματικά δικαιώματα και όροι χρήσης</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δικαιούχος</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 Δημοσθένης Αττέια, thecybersec.gr. Με επιφύλαξη παντός δικαιώματος.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι προστατεύεται</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η αντιστοίχιση των απαιτήσεων με ρυθμίσεις και εργαλεία της Microsoft, οι περιγραφές, τα τεκμήρια, τα σχόλια και η δομή του αρχείου είναι πρωτότυπο έργο του συντάκτη και προστατεύονται από τον ν. 2121/1993. Το κείμενο της Οδηγίας (ΕΕ) 2022/2555 είναι δημόσιο έγγραφο και δεν αποτελεί αντικείμενο αυτής της προστασίας.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι επιτρέπεται</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η χρήση και η συμπλήρωση του αρχείου για τις εσωτερικές ανάγκες του οργανισμού σας, καθώς και η επίδειξή του σε ελεγκτές και αρμόδιες αρχές στο πλαίσιο ελέγχου.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι απαγορεύεται χωρίς γραπτή άδεια του συντάκτη</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η αναδημοσίευση, η αναδιανομή και η ανάρτηση του αρχείου ή τμήματός του σε ιστότοπους, πλατφόρμες ή μέσα κοινωνικής δικτύωσης. Η εμπορική εκμετάλλευση, μαζί με την ενσωμάτωσή του σε προϊόντα, υπηρεσίες, εκπαιδευτικό υλικό ή παραδοτέα προς τρίτους. Η αφαίρεση ή η αλλοίωση της αναφοράς στον συντάκτη και στην πηγή.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πώς το μοιράζεστε</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Με παραπομπή στη σελίδα https://thecybersec.gr/nis2/, από όπου ο καθένας κατεβάζει την τρέχουσα έκδοση.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Επικοινωνία για άδεια χρήσης</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μέσω LinkedIn: https://www.linkedin.com/in/dimosthenisatteia/</t>
   </si>
   <si>
     <t xml:space="preserve">Πώς συμπληρώνεται</t>
@@ -1197,7 +1236,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -1254,13 +1293,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1268,7 +1307,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1276,7 +1315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -1284,7 +1323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1292,7 +1331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1318,7 +1357,7 @@
       </c>
       <c r="B16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1326,7 +1365,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
@@ -1334,7 +1373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -1342,12 +1381,70 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1393,91 +1490,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B2" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="10"/>
@@ -1487,40 +1584,40 @@
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="10"/>
@@ -1530,38 +1627,38 @@
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="10"/>
@@ -1571,36 +1668,36 @@
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
@@ -1610,40 +1707,40 @@
     </row>
     <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
@@ -1653,37 +1750,37 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
@@ -1694,40 +1791,40 @@
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
@@ -1737,40 +1834,40 @@
     </row>
     <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
@@ -1780,38 +1877,38 @@
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
@@ -1821,38 +1918,38 @@
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
@@ -1862,38 +1959,38 @@
     </row>
     <row r="12" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
@@ -1903,40 +2000,40 @@
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
@@ -1946,38 +2043,38 @@
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
@@ -1987,38 +2084,38 @@
     </row>
     <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
@@ -2028,36 +2125,36 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="7" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
@@ -2067,38 +2164,38 @@
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
@@ -2108,38 +2205,38 @@
     </row>
     <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
@@ -2149,38 +2246,38 @@
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
@@ -2190,38 +2287,38 @@
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
@@ -2231,36 +2328,36 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -2270,40 +2367,40 @@
     </row>
     <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
@@ -2313,36 +2410,36 @@
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
@@ -2352,36 +2449,36 @@
     </row>
     <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
@@ -2391,40 +2488,40 @@
     </row>
     <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
@@ -2471,31 +2568,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,7 +2600,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C2" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A2)</f>
@@ -2539,7 +2636,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A3)</f>
@@ -2575,7 +2672,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A4)</f>
@@ -2611,7 +2708,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A5)</f>
@@ -2647,7 +2744,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A6)</f>
@@ -2681,7 +2778,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">SUM(C2:C6)</f>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="235">
   <si>
     <t xml:space="preserve">Οδηγία NIS2 (ΕΕ) 2022/2555 και Microsoft 365: checklist</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t xml:space="preserve">Απόφαση ή πρακτικό του οργάνου διοίκησης. Compliance Manager: βαθμολογία και κατάσταση improvement actions. Secure Score: History.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Purview Compliance Manager premium assessment για το NIS2 (με Microsoft 365 E5 τρία premium assessments είναι δωρεάν)</t>
   </si>
   <si>
     <t xml:space="preserve">Η έγκριση και η ευθύνη είναι οργανωτικό και νομικό ζήτημα. Η Microsoft δίνει μόνο τα στοιχεία πάνω στα οποία αποφασίζει η διοίκηση.</t>
@@ -276,6 +279,9 @@
   </si>
   <si>
     <t xml:space="preserve">Μητρώο κινδύνων και τεκμηρίωση της αναλογικότητας. Secure Score: βαθμολογία και τάση.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το Defender Vulnerability Management και το Microsoft Security Exposure Management</t>
   </si>
   <si>
     <t xml:space="preserve">Η κρίση για το τι είναι «αναλογικό» ανήκει στην οντότητα. Δεν προκύπτει από καμία βαθμολογία.</t>
@@ -320,7 +326,7 @@
     <t xml:space="preserve">Defender XDR: ιστορικό incidents με ταξινόμηση, ανάθεση και χρόνους. Action center για τις ενέργειες αποκατάστασης.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Sentinel (χρέωση με βάση τον όγκο δεδομένων)</t>
+    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο), Microsoft Sentinel (χρέωση με βάση τον όγκο δεδομένων)</t>
   </si>
   <si>
     <t xml:space="preserve">Το πλάνο αντιμετώπισης περιστατικών και οι ρόλοι είναι έγγραφο της οντότητας.</t>
@@ -367,7 +373,7 @@
     <t xml:space="preserve">Defender for Cloud Apps: κατάλογος cloud εφαρμογών σε χρήση. Entra ID: ρυθμίσεις cross-tenant και αποτελέσματα access reviews.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID P2 ή Microsoft Entra ID Governance (access reviews)</t>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery), Microsoft Entra ID P2 ή Microsoft Entra ID Governance (access reviews)</t>
   </si>
   <si>
     <t xml:space="preserve">Οι συμβάσεις και η αξιολόγηση των προμηθευτών είναι οργανωτικά μέτρα.</t>
@@ -393,7 +399,7 @@
     <t xml:space="preserve">Defender Vulnerability Management: exposure score, Weaknesses και κατάσταση remediation. Intune: αναφορές συμμόρφωσης ενημερώσεων.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender for Cloud, GitHub Advanced Security (μόνο αν αναπτύσσετε λογισμικό)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το Defender Vulnerability Management</t>
   </si>
   <si>
     <t xml:space="preserve">Η ασφαλής ανάπτυξη λογισμικού δεν καλύπτεται από το Microsoft 365.</t>
@@ -419,6 +425,9 @@
     <t xml:space="preserve">Εξαγωγές Secure Score και Compliance Manager ανά περίοδο. Εκθέσεις εσωτερικών και εξωτερικών ελέγχων.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Office 365 Plan 2 (Attack simulation training)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Οι δοκιμές παρείσδυσης και οι ανεξάρτητοι έλεγχοι γίνονται από εξειδικευμένο ελεγκτή.</t>
   </si>
   <si>
@@ -484,7 +493,7 @@
     <t xml:space="preserve">Entra ID: πολιτικές Conditional Access, αναθέσεις ρόλων και αποτελέσματα access reviews. Εξαγωγή device inventory.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID P2 (Privileged Identity Management, access reviews)</t>
+    <t xml:space="preserve">Microsoft Entra ID P2 (Privileged Identity Management, access reviews), Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το software inventory</t>
   </si>
   <si>
     <t xml:space="preserve">Η ασφάλεια ανθρώπινων πόρων (έλεγχοι πρόσληψης, πειθαρχική διαδικασία) δεν καλύπτεται από ρύθμιση.</t>
@@ -533,6 +542,9 @@
     <t xml:space="preserve">Φάκελος αξιολόγησης ανά προμηθευτή. Εκθέσεις SOC 2 και ISO 27001 της Microsoft από το Service Trust Portal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Για προμηθευτές που δεν είναι cloud υπηρεσίες δεν υπάρχει εργαλείο Microsoft. Η αξιολόγηση γίνεται με ερωτηματολόγια και συμβατικούς όρους.</t>
   </si>
   <si>
@@ -590,6 +602,9 @@
     <t xml:space="preserve">Threat analytics: αναφορά με τα εκτεθειμένα assets. Αντίγραφο της ενημέρωσης προς τους αποδέκτες.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο) για το Threat analytics</t>
+  </si>
+  <si>
     <t xml:space="preserve">Η ενημέρωση των πελατών είναι οργανωτική διαδικασία.</t>
   </si>
   <si>
@@ -619,6 +634,9 @@
   </si>
   <si>
     <t xml:space="preserve">Εξαγωγή του incident και των αποτελεσμάτων advanced hunting. Αντίγραφο της κοινοποίησης με ώρα υποβολής.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο) για το advanced hunting</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/new-features/defender-for-identity-health-issue-missing-windows-events/
@@ -1566,15 +1584,17 @@
       <c r="H2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="8"/>
+      <c r="I2" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="J2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="10"/>
@@ -1584,7 +1604,7 @@
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>20</v>
@@ -1596,28 +1616,28 @@
         <v>63</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="10"/>
@@ -1627,38 +1647,40 @@
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="8"/>
+        <v>83</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="J4" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="10"/>
@@ -1668,36 +1690,36 @@
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
@@ -1707,40 +1729,40 @@
     </row>
     <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
@@ -1750,37 +1772,37 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
@@ -1791,40 +1813,40 @@
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
@@ -1834,40 +1856,40 @@
     </row>
     <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
@@ -1877,38 +1899,40 @@
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="8"/>
+        <v>128</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="J10" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
@@ -1918,38 +1942,38 @@
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
@@ -1959,38 +1983,38 @@
     </row>
     <row r="12" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
@@ -2000,40 +2024,40 @@
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
@@ -2043,38 +2067,38 @@
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
@@ -2084,38 +2108,40 @@
     </row>
     <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I15" s="8"/>
+        <v>164</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="J15" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
@@ -2125,36 +2151,38 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="I16" s="8"/>
+        <v>171</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="J16" s="8"/>
       <c r="K16" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
@@ -2164,38 +2192,38 @@
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
@@ -2205,38 +2233,40 @@
     </row>
     <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="I18" s="8"/>
+        <v>183</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="J18" s="8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
@@ -2246,38 +2276,38 @@
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
@@ -2287,38 +2317,40 @@
     </row>
     <row r="20" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="8"/>
+        <v>194</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="J20" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
@@ -2328,36 +2360,36 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -2367,40 +2399,40 @@
     </row>
     <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
@@ -2410,36 +2442,36 @@
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
@@ -2449,36 +2481,36 @@
     </row>
     <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
@@ -2488,40 +2520,40 @@
     </row>
     <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
@@ -2574,22 +2606,22 @@
         <v>48</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>35</v>
@@ -2636,7 +2668,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A3)</f>
@@ -2672,7 +2704,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A4)</f>
@@ -2708,7 +2740,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A5)</f>
@@ -2744,7 +2776,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$25,A6)</f>
@@ -2778,7 +2810,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">SUM(C2:C6)</f>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -1263,7 +1263,10 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
-https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,9 @@
       <c r="L3" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
-https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/</t>
+https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
         </is>
       </c>
       <c r="M3" s="26" t="n"/>
@@ -1591,7 +1593,11 @@
           <t>https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
 https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/
 https://thecybersec.gr/posts/entra-tenant-governance-ga/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/kouiz-phishing/</t>
         </is>
       </c>
       <c r="M11" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,8 @@
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>
@@ -1728,7 +1729,8 @@
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M13" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -1269,7 +1269,8 @@
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>
@@ -1397,7 +1398,8 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
-https://thecybersec.gr/posts/gsa-mcp-firewall/</t>
+https://thecybersec.gr/posts/gsa-mcp-firewall/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M8" s="26" t="n"/>
@@ -1730,7 +1732,8 @@
 https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M13" s="26" t="n"/>
@@ -1860,7 +1863,8 @@
         <is>
           <t>https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/gsa-mcp-firewall/</t>
+https://thecybersec.gr/posts/gsa-mcp-firewall/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M15" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -1004,8 +1004,9 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/</t>
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="M2" s="26" t="n"/>
@@ -1196,9 +1197,10 @@
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
 https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
-https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="M5" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
 https://thecybersec.gr/mitroo-politikon/</t>
         </is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
 https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
 https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
 https://thecybersec.gr/mitroo-politikon/</t>
@@ -1272,7 +1272,8 @@
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,8 @@
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
-https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>
@@ -1603,7 +1604,8 @@
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
 https://thecybersec.gr/tekmiriosi-ekpaideysis/
-https://thecybersec.gr/kouiz-phishing/</t>
+https://thecybersec.gr/kouiz-phishing/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="M11" s="26" t="n"/>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,8 @@
       </c>
       <c r="L13" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
@@ -1799,7 +1800,8 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
         </is>

--- a/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-directive-2022-2555-microsoft-365-checklist.xlsx
@@ -1733,7 +1733,8 @@
       </c>
       <c r="L13" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
@@ -1800,7 +1801,8 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
